--- a/test/fixtures/xlsx/record-ref/record-ref.xlsx
+++ b/test/fixtures/xlsx/record-ref/record-ref.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="105">
   <si>
     <t xml:space="preserve">~~table:Item~~</t>
   </si>
@@ -324,6 +324,9 @@
   </si>
   <si>
     <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
   </si>
 </sst>
 </file>
@@ -1394,7 +1397,7 @@
         <v>103</v>
       </c>
       <c r="BA10" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="BB10" t="s">
         <v>16</v>

--- a/test/fixtures/xlsx/record-ref/record-ref.xlsx
+++ b/test/fixtures/xlsx/record-ref/record-ref.xlsx
@@ -12,38 +12,47 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="105">
-  <si>
-    <t xml:space="preserve">~~table:Item~~</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="107">
+  <si>
+    <t xml:space="preserve">:table Item</t>
   </si>
   <si>
     <t xml:space="preserve">What the members point at.</t>
   </si>
   <si>
+    <t xml:space="preserve">:field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:target</t>
+  </si>
+  <si>
     <t xml:space="preserve">index</t>
   </si>
   <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
     <t xml:space="preserve">primary index</t>
   </si>
   <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
     <t xml:space="preserve">cs</t>
   </si>
   <si>
     <t xml:space="preserve">Name</t>
   </si>
   <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
     <t xml:space="preserve">so the row has something in it</t>
   </si>
   <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pad</t>
   </si>
   <si>
@@ -71,49 +80,46 @@
     <t xml:space="preserve">shield</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Loadout~~</t>
+    <t xml:space="preserve">:table Loadout</t>
   </si>
   <si>
     <t xml:space="preserve">A record array whose first member is a reference.</t>
   </si>
   <si>
-    <t xml:space="preserve">Slot1.ItemId</t>
+    <t xml:space="preserve">Slot[0].ItemId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foreign Item</t>
   </si>
   <si>
     <t xml:space="preserve">element 1, the reference</t>
   </si>
   <si>
-    <t xml:space="preserve">foreign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slot1.SwapId</t>
+    <t xml:space="preserve">Slot[0].SwapId</t>
   </si>
   <si>
     <t xml:space="preserve">element 1, a second reference to the same table</t>
   </si>
   <si>
-    <t xml:space="preserve">Slot1.Count</t>
+    <t xml:space="preserve">Slot[0].Count</t>
   </si>
   <si>
     <t xml:space="preserve">element 1, an ordinary member</t>
   </si>
   <si>
-    <t xml:space="preserve">Slot2.ItemId</t>
+    <t xml:space="preserve">Slot[1].ItemId</t>
   </si>
   <si>
     <t xml:space="preserve">element 2, the reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Slot2.SwapId</t>
+    <t xml:space="preserve">Slot[1].SwapId</t>
   </si>
   <si>
     <t xml:space="preserve">element 2, the second reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Slot2.Count</t>
+    <t xml:space="preserve">Slot[1].Count</t>
   </si>
   <si>
     <t xml:space="preserve">element 2, an ordinary member</t>
@@ -128,7 +134,7 @@
     <t xml:space="preserve">30</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Holder~~</t>
+    <t xml:space="preserve">:table Holder</t>
   </si>
   <si>
     <t xml:space="preserve">A single record whose first member is a reference.</t>
@@ -149,67 +155,67 @@
     <t xml:space="preserve">5</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Bag~~</t>
+    <t xml:space="preserve">:table Bag</t>
   </si>
   <si>
     <t xml:space="preserve">One record whose members are arrays, one of them references.</t>
   </si>
   <si>
-    <t xml:space="preserve">Slots.ItemId1</t>
+    <t xml:space="preserve">Slots.ItemId[0]</t>
   </si>
   <si>
     <t xml:space="preserve">element 1 of the member</t>
   </si>
   <si>
-    <t xml:space="preserve">Slots.ItemId2</t>
+    <t xml:space="preserve">Slots.ItemId[1]</t>
   </si>
   <si>
     <t xml:space="preserve">element 2 of the member</t>
   </si>
   <si>
-    <t xml:space="preserve">Slots.Count1</t>
+    <t xml:space="preserve">Slots.Count[0]</t>
   </si>
   <si>
     <t xml:space="preserve">element 1 of the member beside it</t>
   </si>
   <si>
-    <t xml:space="preserve">Slots.Count2</t>
+    <t xml:space="preserve">Slots.Count[1]</t>
   </si>
   <si>
     <t xml:space="preserve">element 2 of the member beside it</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Mount~~</t>
+    <t xml:space="preserve">:table Mount</t>
   </si>
   <si>
     <t xml:space="preserve">A reference inside a record inside a record.</t>
   </si>
   <si>
-    <t xml:space="preserve">Rig1.Core.ItemId</t>
+    <t xml:space="preserve">Rig[0].Core.ItemId</t>
   </si>
   <si>
     <t xml:space="preserve">element 1, two levels in</t>
   </si>
   <si>
-    <t xml:space="preserve">Rig1.Core.Count</t>
+    <t xml:space="preserve">Rig[0].Core.Count</t>
   </si>
   <si>
     <t xml:space="preserve">its sibling at that level</t>
   </si>
   <si>
-    <t xml:space="preserve">Rig2.Core.ItemId</t>
+    <t xml:space="preserve">Rig[1].Core.ItemId</t>
   </si>
   <si>
     <t xml:space="preserve">element 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Rig2.Core.Count</t>
+    <t xml:space="preserve">Rig[1].Core.Count</t>
   </si>
   <si>
     <t xml:space="preserve">its sibling</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Clip~~</t>
+    <t xml:space="preserve">:table Clip</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed by name rather than number.</t>
@@ -233,18 +239,18 @@
     <t xml:space="preserve">24</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Seal~~</t>
+    <t xml:space="preserve">:table Seal</t>
   </si>
   <si>
     <t xml:space="preserve">Keyed by a uuid.</t>
   </si>
   <si>
+    <t xml:space="preserve">uuid</t>
+  </si>
+  <si>
     <t xml:space="preserve">primary index, a uuid</t>
   </si>
   <si>
-    <t xml:space="preserve">uuid</t>
-  </si>
-  <si>
     <t xml:space="preserve">Label</t>
   </si>
   <si>
@@ -260,7 +266,7 @@
     <t xml:space="preserve">beta</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Badge~~</t>
+    <t xml:space="preserve">:table Badge</t>
   </si>
   <si>
     <t xml:space="preserve">A record of one whose members' keys are not numbers.</t>
@@ -269,21 +275,21 @@
     <t xml:space="preserve">Mark.ClipId</t>
   </si>
   <si>
+    <t xml:space="preserve">foreign Clip</t>
+  </si>
+  <si>
     <t xml:space="preserve">a string key, on the run path</t>
   </si>
   <si>
-    <t xml:space="preserve">Clip</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mark.SealId</t>
   </si>
   <si>
+    <t xml:space="preserve">foreign Seal</t>
+  </si>
+  <si>
     <t xml:space="preserve">a uuid key, on the run path</t>
   </si>
   <si>
-    <t xml:space="preserve">Seal</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mark.Rank</t>
   </si>
   <si>
@@ -296,31 +302,31 @@
     <t xml:space="preserve">8</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Pose~~</t>
+    <t xml:space="preserve">:table Pose</t>
   </si>
   <si>
     <t xml:space="preserve">A record member pointing at a table keyed by a string.</t>
   </si>
   <si>
-    <t xml:space="preserve">Step1.ClipId</t>
+    <t xml:space="preserve">Step[0].ClipId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foreign Clip?</t>
   </si>
   <si>
     <t xml:space="preserve">element 1, a string key</t>
   </si>
   <si>
-    <t xml:space="preserve">foreign?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Step1.Weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Step2.ClipId</t>
+    <t xml:space="preserve">Step[0].Weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step[1].ClipId</t>
   </si>
   <si>
     <t xml:space="preserve">element 2, a string key</t>
   </si>
   <si>
-    <t xml:space="preserve">Step2.Weight</t>
+    <t xml:space="preserve">Step[1].Weight</t>
   </si>
   <si>
     <t xml:space="preserve">3</t>
@@ -371,199 +377,391 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:BR10"/>
+  <dimension ref="B2:BS8"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
       </c>
       <c r="R2" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="S2" t="s">
+        <v>41</v>
       </c>
       <c r="Z2" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>48</v>
       </c>
       <c r="AH2" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>58</v>
       </c>
       <c r="AP2" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>68</v>
       </c>
       <c r="AX2" t="s">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>97</v>
       </c>
       <c r="BF2" t="s">
-        <v>73</v>
+        <v>75</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>76</v>
       </c>
       <c r="BN2" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>35</v>
       </c>
       <c r="R3" t="s">
-        <v>39</v>
+        <v>2</v>
+      </c>
+      <c r="S3" t="s">
+        <v>6</v>
+      </c>
+      <c r="T3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V3" t="s">
+        <v>13</v>
+      </c>
+      <c r="W3" t="s">
+        <v>15</v>
       </c>
       <c r="Z3" t="s">
-        <v>46</v>
+        <v>2</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>55</v>
       </c>
       <c r="AH3" t="s">
-        <v>56</v>
+        <v>2</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>65</v>
       </c>
       <c r="AP3" t="s">
-        <v>66</v>
+        <v>2</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>16</v>
       </c>
       <c r="AX3" t="s">
-        <v>95</v>
+        <v>2</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>98</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>101</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>102</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>104</v>
       </c>
       <c r="BF3" t="s">
-        <v>74</v>
+        <v>2</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>6</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>79</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>13</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>15</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>16</v>
       </c>
       <c r="BN3" t="s">
-        <v>83</v>
+        <v>2</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>6</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>86</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>89</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>92</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
       </c>
       <c r="J4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="L4" t="s">
         <v>25</v>
       </c>
       <c r="M4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="O4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="P4" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>7</v>
       </c>
       <c r="R4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S4" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="T4" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="U4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V4" t="s">
-        <v>12</v>
+        <v>7</v>
+      </c>
+      <c r="W4" t="s">
+        <v>7</v>
       </c>
       <c r="Z4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="AB4" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="AC4" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="AD4" t="s">
-        <v>53</v>
+        <v>7</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>7</v>
       </c>
       <c r="AH4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="AJ4" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="AK4" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="AL4" t="s">
-        <v>63</v>
+        <v>25</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>7</v>
       </c>
       <c r="AP4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ4" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AS4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="s">
-        <v>13</v>
+        <v>7</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>7</v>
       </c>
       <c r="AX4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY4" t="s">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="AZ4" t="s">
         <v>99</v>
       </c>
       <c r="BA4" t="s">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="s">
-        <v>102</v>
+        <v>99</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>7</v>
       </c>
       <c r="BF4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BG4" t="s">
         <v>77</v>
       </c>
       <c r="BH4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BI4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BJ4" t="s">
-        <v>13</v>
+        <v>7</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>7</v>
       </c>
       <c r="BN4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BO4" t="s">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="BP4" t="s">
         <v>87</v>
@@ -572,30 +770,36 @@
         <v>90</v>
       </c>
       <c r="BR4" t="s">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -612,26 +816,32 @@
       <c r="P5" t="s">
         <v>34</v>
       </c>
+      <c r="Q5" t="s">
+        <v>36</v>
+      </c>
       <c r="R5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="T5" t="s">
         <v>43</v>
       </c>
       <c r="U5" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="V5" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="W5" t="s">
+        <v>14</v>
       </c>
       <c r="Z5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="AB5" t="s">
         <v>50</v>
@@ -642,11 +852,14 @@
       <c r="AD5" t="s">
         <v>54</v>
       </c>
+      <c r="AE5" t="s">
+        <v>56</v>
+      </c>
       <c r="AH5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="AJ5" t="s">
         <v>60</v>
@@ -657,56 +870,68 @@
       <c r="AL5" t="s">
         <v>64</v>
       </c>
+      <c r="AM5" t="s">
+        <v>66</v>
+      </c>
       <c r="AP5" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>4</v>
+      </c>
+      <c r="AY5" t="s">
         <v>8</v>
       </c>
-      <c r="AR5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>3</v>
-      </c>
-      <c r="AY5" t="s">
-        <v>97</v>
-      </c>
       <c r="AZ5" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="BA5" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="BB5" t="s">
-        <v>34</v>
+        <v>103</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>36</v>
       </c>
       <c r="BF5" t="s">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="BG5" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>12</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>14</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>14</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO5" t="s">
         <v>8</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>11</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>11</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>11</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>3</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>85</v>
       </c>
       <c r="BP5" t="s">
         <v>88</v>
@@ -715,722 +940,466 @@
         <v>91</v>
       </c>
       <c r="BR5" t="s">
-        <v>11</v>
+        <v>93</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
       </c>
       <c r="J6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="L6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="M6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="O6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="P6" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>9</v>
       </c>
       <c r="R6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="T6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V6" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="W6" t="s">
+        <v>9</v>
       </c>
       <c r="Z6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="AB6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>9</v>
       </c>
       <c r="AH6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="AJ6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AK6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="AL6" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>9</v>
       </c>
       <c r="AP6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AQ6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AS6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>9</v>
       </c>
       <c r="AX6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY6" t="s">
-        <v>98</v>
+        <v>9</v>
       </c>
       <c r="AZ6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BA6" t="s">
-        <v>98</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>9</v>
       </c>
       <c r="BF6" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="BG6" t="s">
         <v>9</v>
       </c>
       <c r="BH6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BI6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BJ6" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>9</v>
       </c>
       <c r="BN6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BO6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="BP6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="BQ6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BR6" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J7" t="s">
-        <v>5</v>
+        <v>19</v>
+      </c>
+      <c r="G7" t="s">
+        <v>19</v>
       </c>
       <c r="K7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="M7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N7" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="O7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P7" t="s">
-        <v>5</v>
-      </c>
-      <c r="R7" t="s">
-        <v>5</v>
+        <v>17</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>38</v>
       </c>
       <c r="S7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="T7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="U7" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="V7" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>5</v>
+        <v>19</v>
+      </c>
+      <c r="W7" t="s">
+        <v>19</v>
       </c>
       <c r="AA7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AB7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AC7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AD7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>5</v>
+        <v>37</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>38</v>
       </c>
       <c r="AI7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AJ7" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AK7" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="AL7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>5</v>
+        <v>20</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>38</v>
       </c>
       <c r="AQ7" t="s">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="AR7" t="s">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="AS7" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AT7" t="s">
-        <v>5</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>5</v>
+        <v>19</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>19</v>
       </c>
       <c r="AY7" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="AZ7" t="s">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="BA7" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="BB7" t="s">
-        <v>5</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>5</v>
+        <v>73</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>20</v>
       </c>
       <c r="BG7" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="BH7" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="BI7" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="BJ7" t="s">
-        <v>5</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>5</v>
+        <v>19</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>19</v>
       </c>
       <c r="BO7" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="BP7" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="BQ7" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="BR7" t="s">
-        <v>5</v>
+        <v>94</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>6</v>
-      </c>
-      <c r="J8" t="s">
-        <v>6</v>
+        <v>19</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
       </c>
       <c r="K8" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="L8" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M8" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="O8" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="P8" t="s">
-        <v>6</v>
-      </c>
-      <c r="R8" t="s">
-        <v>6</v>
+        <v>19</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>19</v>
       </c>
       <c r="S8" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T8" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="U8" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="V8" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>6</v>
+        <v>19</v>
+      </c>
+      <c r="W8" t="s">
+        <v>19</v>
       </c>
       <c r="AA8" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AB8" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AC8" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AD8" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>6</v>
+        <v>39</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>19</v>
       </c>
       <c r="AI8" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AJ8" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AK8" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="AL8" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>6</v>
+        <v>19</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>19</v>
       </c>
       <c r="AQ8" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="AR8" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="AS8" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AT8" t="s">
-        <v>6</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>6</v>
+        <v>19</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>19</v>
       </c>
       <c r="AY8" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AZ8" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="BA8" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="BB8" t="s">
-        <v>6</v>
-      </c>
-      <c r="BF8" t="s">
-        <v>6</v>
+        <v>106</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>19</v>
       </c>
       <c r="BG8" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="BH8" t="s">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="BI8" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="BJ8" t="s">
-        <v>6</v>
-      </c>
-      <c r="BN8" t="s">
-        <v>6</v>
+        <v>19</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>19</v>
       </c>
       <c r="BO8" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BP8" t="s">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="BQ8" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="BR8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M9" t="s">
-        <v>35</v>
-      </c>
-      <c r="N9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O9" t="s">
-        <v>14</v>
-      </c>
-      <c r="P9" t="s">
-        <v>36</v>
-      </c>
-      <c r="R9" t="s">
-        <v>14</v>
-      </c>
-      <c r="S9" t="s">
-        <v>17</v>
-      </c>
-      <c r="T9" t="s">
-        <v>44</v>
-      </c>
-      <c r="U9" t="s">
-        <v>16</v>
-      </c>
-      <c r="V9" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>17</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>16</v>
-      </c>
-      <c r="AS9" t="s">
-        <v>16</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>16</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>14</v>
-      </c>
-      <c r="AY9" t="s">
-        <v>69</v>
-      </c>
-      <c r="AZ9" t="s">
-        <v>14</v>
-      </c>
-      <c r="BA9" t="s">
-        <v>71</v>
-      </c>
-      <c r="BB9" t="s">
-        <v>17</v>
-      </c>
-      <c r="BF9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>79</v>
-      </c>
-      <c r="BH9" t="s">
-        <v>16</v>
-      </c>
-      <c r="BI9" t="s">
-        <v>16</v>
-      </c>
-      <c r="BJ9" t="s">
-        <v>16</v>
-      </c>
-      <c r="BN9" t="s">
-        <v>14</v>
-      </c>
-      <c r="BO9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BP9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BQ9" t="s">
-        <v>92</v>
-      </c>
-      <c r="BR9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L10" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" t="s">
-        <v>37</v>
-      </c>
-      <c r="N10" t="s">
-        <v>16</v>
-      </c>
-      <c r="O10" t="s">
-        <v>16</v>
-      </c>
-      <c r="P10" t="s">
-        <v>16</v>
-      </c>
-      <c r="R10" t="s">
-        <v>17</v>
-      </c>
-      <c r="S10" t="s">
-        <v>16</v>
-      </c>
-      <c r="T10" t="s">
-        <v>16</v>
-      </c>
-      <c r="U10" t="s">
-        <v>16</v>
-      </c>
-      <c r="V10" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>16</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>17</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>37</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>16</v>
-      </c>
-      <c r="AP10" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>16</v>
-      </c>
-      <c r="AS10" t="s">
-        <v>16</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>16</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>17</v>
-      </c>
-      <c r="AY10" t="s">
-        <v>71</v>
-      </c>
-      <c r="AZ10" t="s">
-        <v>103</v>
-      </c>
-      <c r="BA10" t="s">
-        <v>104</v>
-      </c>
-      <c r="BB10" t="s">
-        <v>16</v>
-      </c>
-      <c r="BF10" t="s">
-        <v>80</v>
-      </c>
-      <c r="BG10" t="s">
-        <v>81</v>
-      </c>
-      <c r="BH10" t="s">
-        <v>16</v>
-      </c>
-      <c r="BI10" t="s">
-        <v>16</v>
-      </c>
-      <c r="BJ10" t="s">
-        <v>16</v>
-      </c>
-      <c r="BN10" t="s">
-        <v>17</v>
-      </c>
-      <c r="BO10" t="s">
-        <v>69</v>
-      </c>
-      <c r="BP10" t="s">
-        <v>78</v>
-      </c>
-      <c r="BQ10" t="s">
-        <v>93</v>
-      </c>
-      <c r="BR10" t="s">
-        <v>16</v>
+        <v>95</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
